--- a/cvs-review/cvs-metrics-v0_2026-10-09.xlsx
+++ b/cvs-review/cvs-metrics-v0_2026-10-09.xlsx
@@ -45,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
+        <fgColor rgb="000F172A"/>
       </patternFill>
     </fill>
     <fill>

--- a/cvs-review/cvs-metrics-v0_2026-10-09.xlsx
+++ b/cvs-review/cvs-metrics-v0_2026-10-09.xlsx
@@ -45,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
